--- a/ResourcesBD/productPrice.xlsx
+++ b/ResourcesBD/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="60">
   <si>
     <t>Code*</t>
   </si>
@@ -160,6 +160,45 @@
   </si>
   <si>
     <t>2025-10-27</t>
+  </si>
+  <si>
+    <t>2025-11-12</t>
+  </si>
+  <si>
+    <t>2025-11-14</t>
+  </si>
+  <si>
+    <t>2025-11-18</t>
+  </si>
+  <si>
+    <t>2025-11-19</t>
+  </si>
+  <si>
+    <t>2025-11-20</t>
+  </si>
+  <si>
+    <t>2025-11-24</t>
+  </si>
+  <si>
+    <t>2025-11-25</t>
+  </si>
+  <si>
+    <t>2025-11-26</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
   </si>
 </sst>
 </file>
@@ -563,19 +602,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>9801.0</v>
+        <v>3529.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>2148.0</v>
+        <v>7082.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>8078.0</v>
+        <v>1014.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>4502.0</v>
+        <v>3962.0</v>
       </c>
       <c r="N2" s="1">
         <v>0</v>
@@ -613,19 +652,19 @@
         <v>25</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>9228.0</v>
+        <v>8349.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>4300.0</v>
+        <v>9643.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>7465.0</v>
+        <v>5355.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>8704.0</v>
+        <v>5859.0</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>

--- a/ResourcesBD/productPrice.xlsx
+++ b/ResourcesBD/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="62">
   <si>
     <t>Code*</t>
   </si>
@@ -199,6 +199,12 @@
   </si>
   <si>
     <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>2025-12-16</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
   </si>
 </sst>
 </file>
@@ -602,19 +608,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>3529.0</v>
+        <v>5981.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>7082.0</v>
+        <v>8457.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>1014.0</v>
+        <v>4776.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>3962.0</v>
+        <v>2032.0</v>
       </c>
       <c r="N2" s="1">
         <v>0</v>
@@ -652,19 +658,19 @@
         <v>25</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>8349.0</v>
+        <v>6842.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>9643.0</v>
+        <v>8145.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>5355.0</v>
+        <v>4427.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>5859.0</v>
+        <v>3775.0</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>

--- a/ResourcesBD/productPrice.xlsx
+++ b/ResourcesBD/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="63">
   <si>
     <t>Code*</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>2025-12-17</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
   </si>
 </sst>
 </file>
@@ -608,19 +611,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>5981.0</v>
+        <v>2583.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>8457.0</v>
+        <v>7839.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>4776.0</v>
+        <v>8781.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>2032.0</v>
+        <v>5064.0</v>
       </c>
       <c r="N2" s="1">
         <v>0</v>
@@ -658,19 +661,19 @@
         <v>25</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>6842.0</v>
+        <v>1948.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>8145.0</v>
+        <v>6846.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>4427.0</v>
+        <v>3978.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>3775.0</v>
+        <v>7984.0</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>

--- a/ResourcesBD/productPrice.xlsx
+++ b/ResourcesBD/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="64">
   <si>
     <t>Code*</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
   </si>
 </sst>
 </file>
@@ -611,19 +614,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>2583.0</v>
+        <v>5988.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>7839.0</v>
+        <v>1327.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>8781.0</v>
+        <v>1736.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>5064.0</v>
+        <v>9885.0</v>
       </c>
       <c r="N2" s="1">
         <v>0</v>
@@ -661,19 +664,19 @@
         <v>25</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>1948.0</v>
+        <v>6049.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>6846.0</v>
+        <v>7104.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>3978.0</v>
+        <v>5264.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>7984.0</v>
+        <v>8725.0</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>

--- a/ResourcesBD/productPrice.xlsx
+++ b/ResourcesBD/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="66">
   <si>
     <t>Code*</t>
   </si>
@@ -211,6 +211,12 @@
   </si>
   <si>
     <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
   </si>
 </sst>
 </file>
@@ -614,19 +620,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>5988.0</v>
+        <v>5856.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>1327.0</v>
+        <v>1976.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>1736.0</v>
+        <v>3637.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>9885.0</v>
+        <v>9912.0</v>
       </c>
       <c r="N2" s="1">
         <v>0</v>
@@ -664,19 +670,19 @@
         <v>25</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>6049.0</v>
+        <v>2510.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>7104.0</v>
+        <v>2369.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>5264.0</v>
+        <v>3938.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>8725.0</v>
+        <v>6918.0</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>

--- a/ResourcesBD/productPrice.xlsx
+++ b/ResourcesBD/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>Code*</t>
   </si>
@@ -99,124 +99,13 @@
     <t>12.00</t>
   </si>
   <si>
-    <t>2027-10-07</t>
-  </si>
-  <si>
-    <t>2027-10-08</t>
-  </si>
-  <si>
-    <t>2025-10-07</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>5301</t>
-  </si>
-  <si>
-    <t>4593</t>
-  </si>
-  <si>
-    <t>3151</t>
-  </si>
-  <si>
-    <t>3363</t>
-  </si>
-  <si>
-    <t>6980</t>
-  </si>
-  <si>
-    <t>9287</t>
-  </si>
-  <si>
-    <t>3015</t>
-  </si>
-  <si>
-    <t>6669</t>
-  </si>
-  <si>
-    <t>2025-10-14</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>2025-10-16</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>2025-10-20</t>
-  </si>
-  <si>
-    <t>2025-10-21</t>
-  </si>
-  <si>
-    <t>2025-10-22</t>
-  </si>
-  <si>
-    <t>2025-10-27</t>
-  </si>
-  <si>
-    <t>2025-11-12</t>
-  </si>
-  <si>
-    <t>2025-11-14</t>
-  </si>
-  <si>
-    <t>2025-11-18</t>
-  </si>
-  <si>
-    <t>2025-11-19</t>
-  </si>
-  <si>
-    <t>2025-11-20</t>
-  </si>
-  <si>
-    <t>2025-11-24</t>
-  </si>
-  <si>
-    <t>2025-11-25</t>
-  </si>
-  <si>
-    <t>2025-11-26</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>9662</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
   </si>
 </sst>
 </file>
@@ -253,10 +142,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,7 +431,9 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="9" max="9" customWidth="true" width="11.1796875"/>
-    <col min="10" max="16" style="1" width="8.0"/>
+    <col min="10" max="13" style="1" width="8.0"/>
+    <col min="14" max="14" customWidth="true" style="1" width="9.26953125"/>
+    <col min="15" max="16" style="1" width="8.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -620,25 +512,25 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>5856.0</v>
+        <v>28</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>6092.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>1976.0</v>
+        <v>8753.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>3637.0</v>
+        <v>3930.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>9912.0</v>
+        <v>4314.0</v>
       </c>
       <c r="N2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="1">
         <v>15</v>
@@ -670,25 +562,25 @@
         <v>25</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>2510.0</v>
+        <v>3708.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>2369.0</v>
+        <v>1266.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>3938.0</v>
+        <v>8430.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>6918.0</v>
+        <v>3060.0</v>
       </c>
       <c r="N3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="1">
         <v>15</v>
@@ -696,5 +588,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ResourcesBD/productPrice.xlsx
+++ b/ResourcesBD/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
   <si>
     <t>Code*</t>
   </si>
@@ -106,6 +106,27 @@
   </si>
   <si>
     <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
   </si>
 </sst>
 </file>
@@ -512,19 +533,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>6092.0</v>
+        <v>7635.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>8753.0</v>
+        <v>6927.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>3930.0</v>
+        <v>1951.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>4314.0</v>
+        <v>1667.0</v>
       </c>
       <c r="N2" s="1">
         <v>1</v>
@@ -562,19 +583,19 @@
         <v>25</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>3708.0</v>
+        <v>3967.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>1266.0</v>
+        <v>2408.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>8430.0</v>
+        <v>8542.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>3060.0</v>
+        <v>8052.0</v>
       </c>
       <c r="N3" s="1">
         <v>1</v>
